--- a/output/pdf_financials_xlsx/RIO.xlsx
+++ b/output/pdf_financials_xlsx/RIO.xlsx
@@ -942,16 +942,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8.2705</v>
+        <v>-8.2705</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>10.392532</v>
+        <v>-10.392532</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>10.541403</v>
+        <v>-10.509265</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.336478</v>
+        <v>-2.270444</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>12.34</v>
@@ -993,7 +993,7 @@
         <v>-0.013</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-27.284</v>
       </c>
     </row>
     <row r="18">
@@ -1102,25 +1102,25 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>8.2705</v>
+        <v>-8.2705</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>10.392532</v>
+        <v>-10.392532</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10.525334</v>
+        <v>-10.525334</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.303461</v>
+        <v>-2.303461</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>12.356</v>
+        <v>-12.356</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.021</v>
+        <v>-0.021</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>13.642</v>
+        <v>-13.642</v>
       </c>
     </row>
     <row r="21">
@@ -1199,25 +1199,25 @@
         <v>-5.675805</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8.2705</v>
+        <v>-8.2705</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>10.392532</v>
+        <v>-10.392532</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>10.525334</v>
+        <v>-10.525334</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.303461</v>
+        <v>-2.303461</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>12.356</v>
+        <v>-12.356</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.021</v>
+        <v>-0.021</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>13.642</v>
+        <v>-13.642</v>
       </c>
     </row>
     <row r="24">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>51.690625</v>
+        <v>-51.690625</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>148.464743</v>
+        <v>-148.464743</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>210.50668</v>
+        <v>-210.50668</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>247.12</v>
+        <v>-247.12</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>454.733333</v>
+        <v>-454.733333</v>
       </c>
     </row>
     <row r="27">
@@ -1335,16 +1335,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.2705</v>
+        <v>-8.2705</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>10.392532</v>
+        <v>-10.392532</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>10.541403</v>
+        <v>-10.509265</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.336478</v>
+        <v>-2.270444</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>12.34</v>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.2705</v>
+        <v>-8.2705</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>10.392532</v>
+        <v>-10.392532</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10.541403</v>
+        <v>-10.509265</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.336478</v>
+        <v>-2.270444</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>14.374</v>
@@ -1481,16 +1481,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.1524370143139391</v>
+        <v>-0.1529031763876922</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.413109817426057</v>
+        <v>-1.454208956486044</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.1296596434359805</v>
@@ -1499,7 +1499,7 @@
         <v>162.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -3417,28 +3417,28 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.624368</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.959468</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>8.242120999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>9.081203</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>10.609506</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>11.61</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>10.358</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>10.756</v>
       </c>
     </row>
     <row r="93">
@@ -6218,7 +6218,11 @@
           <t>Reserves (Note 15)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -7050,7 +7054,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -8030,7 +8038,11 @@
           <t>Reserves (Note 16)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -8760,7 +8772,11 @@
           <t>Reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>2.624368</v>
       </c>
@@ -15208,10 +15224,10 @@
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.021</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>13.642</v>
+        <v>-13.642</v>
       </c>
     </row>
     <row r="188">
@@ -15322,10 +15338,10 @@
         </is>
       </c>
       <c r="K189" s="5" t="n">
-        <v>10.785</v>
+        <v>-10.785</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>13.642</v>
+        <v>-13.642</v>
       </c>
     </row>
     <row r="190">
@@ -17231,10 +17247,10 @@
         </is>
       </c>
       <c r="J224" s="5" t="n">
-        <v>12.356</v>
+        <v>-12.356</v>
       </c>
       <c r="K224" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.021</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -17333,16 +17349,16 @@
         </is>
       </c>
       <c r="H226" s="5" t="n">
-        <v>10.557489</v>
+        <v>-10.557489</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>9.389037</v>
+        <v>-9.389037</v>
       </c>
       <c r="J226" s="5" t="n">
-        <v>9.901999999999999</v>
+        <v>-9.901999999999999</v>
       </c>
       <c r="K226" s="5" t="n">
-        <v>10.785</v>
+        <v>-10.785</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -18865,13 +18881,13 @@
         </is>
       </c>
       <c r="H254" s="5" t="n">
-        <v>10.525334</v>
+        <v>-10.525334</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>2.303461</v>
+        <v>-2.303461</v>
       </c>
       <c r="J254" s="5" t="n">
-        <v>12.355712</v>
+        <v>-12.355712</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -18980,10 +18996,10 @@
         </is>
       </c>
       <c r="I256" s="5" t="n">
-        <v>9.389037</v>
+        <v>-9.389037</v>
       </c>
       <c r="J256" s="5" t="n">
-        <v>9.902265999999999</v>
+        <v>-9.902265999999999</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -19743,10 +19759,10 @@
         </is>
       </c>
       <c r="F270" s="5" t="n">
-        <v>8.2705</v>
+        <v>-8.2705</v>
       </c>
       <c r="G270" s="5" t="n">
-        <v>10.392532</v>
+        <v>-10.392532</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RIO.xlsx
+++ b/output/pdf_financials_xlsx/RIO.xlsx
@@ -810,25 +810,25 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022688</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.123611</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015256</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.053685</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.245</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.659</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.893</v>
       </c>
     </row>
     <row r="13">
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-8.2705</v>
+        <v>-8.247812</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-10.392532</v>
+        <v>-10.268921</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-10.509265</v>
+        <v>-10.494009</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.270444</v>
+        <v>-2.216759</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.34</v>
+        <v>12.585</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.008</v>
+        <v>0.667</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>13.642</v>
+        <v>14.535</v>
       </c>
     </row>
     <row r="28">
@@ -1401,25 +1401,25 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.2705</v>
+        <v>-8.247812</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-10.392532</v>
+        <v>-10.268921</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-10.509265</v>
+        <v>-10.494009</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.270444</v>
+        <v>-2.216759</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>14.374</v>
+        <v>14.619</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.25</v>
+        <v>0.909</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>13.845</v>
+        <v>14.738</v>
       </c>
     </row>
     <row r="30">
@@ -1563,19 +1563,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.33776</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.101566</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.410836</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>21.345286</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.679667</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>4.596</v>
@@ -1625,19 +1625,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>4</v>
+        <v>5.33776</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.101566</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>14.060407</v>
+        <v>19.471243</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.046</v>
+        <v>21.391286</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.046</v>
+        <v>4.725667</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>4.642</v>
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.49002</v>
+        <v>0.15226</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.201778</v>
+        <v>0.100212</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.535698</v>
+        <v>0.124862</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>23.069873</v>
+        <v>1.724587</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.204553</v>
+        <v>0.524886</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.252</v>
@@ -4455,16 +4455,16 @@
         </is>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.264484</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.181</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.155</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.151</v>
       </c>
     </row>
     <row r="125">
@@ -4488,16 +4488,16 @@
         </is>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.264484</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.181</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.155</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.151</v>
       </c>
     </row>
     <row r="126">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
@@ -11294,7 +11294,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -13140,7 +13144,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -14624,7 +14632,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -19140,7 +19148,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">

--- a/output/pdf_financials_xlsx/RIO.xlsx
+++ b/output/pdf_financials_xlsx/RIO.xlsx
@@ -638,19 +638,19 @@
         <v>0.271643</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.226571</v>
+        <v>0.329571</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.232388</v>
+        <v>1.443856</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.269876</v>
+        <v>1.417982</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.837</v>
+        <v>0.98</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.495</v>
+        <v>1.646</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0</v>
@@ -740,16 +740,16 @@
         <v>9.284183000000001</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.232388</v>
+        <v>1.443856</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.269876</v>
+        <v>1.417982</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.837</v>
+        <v>0.98</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.495</v>
+        <v>1.646</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.126084</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.250565</v>
+        <v>0.376649</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0</v>
@@ -2009,7 +2009,7 @@
         <v>1.724587</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.524886</v>
+        <v>0.398802</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.252</v>
@@ -2614,25 +2614,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.057968</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.713442</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.164775</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -14184,7 +14184,11 @@
           <t>Net proceeds from private placement</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E169" s="5" t="n">
         <v>7.439412</v>
       </c>
@@ -16520,7 +16524,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
